--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-observation-other-quantities.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-observation-other-quantities.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2607" uniqueCount="553">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2607" uniqueCount="554">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-26T07:28:06+00:00</t>
+    <t>2026-10-21T09:39:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -87,7 +87,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This FHIR profile can be used for all the other Observations for PreNUDGE, beeing quantities and not fitting the existing narrow standardized observations. If some code for specifying a new Observation is missing, please contact prenudge@joanneum.at.</t>
+    <t>This FHIR profile can be used for all the other Observations for PreNUDGE, being quantities and not fitting the existing narrow standardized observations. If some code for specifying a new Observation is missing, please contact prenudge@joanneum.at.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -1503,6 +1503,10 @@
   <si>
     <t xml:space="preserve">obs-3
 </t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+sqty-1:The comparator is not used on a SimpleQuantity {comparator.empty()}</t>
   </si>
   <si>
     <t>OBX-7</t>
@@ -8241,7 +8245,7 @@
         <v>477</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>105</v>
+        <v>478</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>21</v>
@@ -8250,10 +8254,10 @@
         <v>21</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>21</v>
@@ -8264,10 +8268,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8293,10 +8297,10 @@
         <v>474</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -8347,7 +8351,7 @@
         <v>21</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>81</v>
@@ -8359,7 +8363,7 @@
         <v>477</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>105</v>
+        <v>478</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>21</v>
@@ -8368,10 +8372,10 @@
         <v>21</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>21</v>
@@ -8382,10 +8386,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8411,16 +8415,16 @@
         <v>182</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="O53" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>21</v>
@@ -8448,10 +8452,10 @@
         <v>117</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>21</v>
@@ -8469,7 +8473,7 @@
         <v>21</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>81</v>
@@ -8487,10 +8491,10 @@
         <v>21</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>410</v>
@@ -8504,10 +8508,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8533,16 +8537,16 @@
         <v>182</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>21</v>
@@ -8570,10 +8574,10 @@
         <v>424</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>21</v>
@@ -8591,7 +8595,7 @@
         <v>21</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>81</v>
@@ -8609,10 +8613,10 @@
         <v>21</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>410</v>
@@ -8626,10 +8630,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8652,17 +8656,17 @@
         <v>21</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>21</v>
@@ -8711,7 +8715,7 @@
         <v>21</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>81</v>
@@ -8735,7 +8739,7 @@
         <v>21</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>21</v>
@@ -8746,10 +8750,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8775,10 +8779,10 @@
         <v>160</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -8829,7 +8833,7 @@
         <v>21</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>81</v>
@@ -8850,10 +8854,10 @@
         <v>21</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>21</v>
@@ -8864,10 +8868,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8890,16 +8894,16 @@
         <v>94</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -8949,7 +8953,7 @@
         <v>21</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>81</v>
@@ -8970,10 +8974,10 @@
         <v>21</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>21</v>
@@ -8984,10 +8988,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9010,16 +9014,16 @@
         <v>94</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -9069,7 +9073,7 @@
         <v>21</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>81</v>
@@ -9090,10 +9094,10 @@
         <v>21</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>21</v>
@@ -9104,10 +9108,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9133,16 +9137,16 @@
         <v>458</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="O59" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>21</v>
@@ -9191,7 +9195,7 @@
         <v>21</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>81</v>
@@ -9212,10 +9216,10 @@
         <v>21</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>21</v>
@@ -9226,10 +9230,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9344,10 +9348,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9464,10 +9468,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9586,10 +9590,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9615,13 +9619,13 @@
         <v>182</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="O63" t="s" s="2">
         <v>268</v>
@@ -9652,10 +9656,10 @@
         <v>424</v>
       </c>
       <c r="Y63" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="Z63" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>21</v>
@@ -9673,7 +9677,7 @@
         <v>21</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>93</v>
@@ -9691,7 +9695,7 @@
         <v>21</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="AM63" t="s" s="2">
         <v>272</v>
@@ -9708,10 +9712,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9734,16 +9738,16 @@
         <v>94</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="M64" t="s" s="2">
         <v>339</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="O64" t="s" s="2">
         <v>341</v>
@@ -9795,7 +9799,7 @@
         <v>21</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>81</v>
@@ -9813,7 +9817,7 @@
         <v>21</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="AM64" t="s" s="2">
         <v>344</v>
@@ -9830,10 +9834,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9859,13 +9863,13 @@
         <v>182</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="O65" t="s" s="2">
         <v>395</v>
@@ -9917,7 +9921,7 @@
         <v>21</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>81</v>
@@ -9952,10 +9956,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10039,7 +10043,7 @@
         <v>21</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>81</v>
@@ -10074,10 +10078,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10103,10 +10107,10 @@
         <v>83</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="N67" t="s" s="2">
         <v>461</v>
@@ -10161,7 +10165,7 @@
         <v>21</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>81</v>
